--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -4307,7 +4307,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118485828</v>
+        <v>118486241</v>
       </c>
       <c r="B34" t="n">
         <v>97846</v>
@@ -4355,14 +4355,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A  1370, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>570161</v>
+        <v>570165</v>
       </c>
       <c r="R34" t="n">
-        <v>6426067</v>
+        <v>6426120</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118486241</v>
+        <v>118485828</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4470,14 +4470,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A  1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>570165</v>
+        <v>570161</v>
       </c>
       <c r="R35" t="n">
-        <v>6426120</v>
+        <v>6426067</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -4307,7 +4307,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118486241</v>
+        <v>118485828</v>
       </c>
       <c r="B34" t="n">
         <v>97846</v>
@@ -4355,14 +4355,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A  1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>570165</v>
+        <v>570161</v>
       </c>
       <c r="R34" t="n">
-        <v>6426120</v>
+        <v>6426067</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118485828</v>
+        <v>118486241</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4470,14 +4470,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A  1370, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>570161</v>
+        <v>570165</v>
       </c>
       <c r="R35" t="n">
-        <v>6426067</v>
+        <v>6426120</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -4310,7 +4310,7 @@
         <v>118485828</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>118486241</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -2516,7 +2516,7 @@
         <v>114545660</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -2516,7 +2516,7 @@
         <v>114545660</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -2516,7 +2516,7 @@
         <v>114545660</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -2516,7 +2516,7 @@
         <v>114545660</v>
       </c>
       <c r="B18" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 1182-2024 artfynd.xlsx
+++ b/artfynd/A 1182-2024 artfynd.xlsx
@@ -2516,7 +2516,7 @@
         <v>114545660</v>
       </c>
       <c r="B18" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
